--- a/files/九龙-九龙塘-Park College.xlsx
+++ b/files/九龙-九龙塘-Park College.xlsx
@@ -1428,7 +1428,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1713,7 +1713,7 @@
           <t>GV | 3060呎 (4+房)
 $14880万
 $48,627/呎
-(26年-08月-19日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>
